--- a/Result/profitability/8255.xlsx
+++ b/Result/profitability/8255.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.65</v>
+        <v>1.5625</v>
       </c>
       <c r="N2" t="n">
-        <v>28.13375</v>
+        <v>27.61125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>1.52125</v>
+        <v>1.48375</v>
       </c>
       <c r="N3" t="n">
-        <v>27.90625</v>
+        <v>27.59625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>1.43375</v>
+        <v>1.32375</v>
       </c>
       <c r="N4" t="n">
-        <v>27.85125</v>
+        <v>27.6225</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.22625</v>
+        <v>1.35875</v>
       </c>
       <c r="N5" t="n">
-        <v>27.61125</v>
+        <v>27.54375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>1.25875</v>
+        <v>1.195</v>
       </c>
       <c r="N6" t="n">
-        <v>27.80375</v>
+        <v>28.16375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17125</v>
+        <v>1.1425</v>
       </c>
       <c r="N7" t="n">
-        <v>28.99125</v>
+        <v>29.055</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.0875</v>
       </c>
       <c r="N8" t="n">
-        <v>30.29625</v>
+        <v>30.30125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1483</v>
+      </c>
+      <c r="E75" t="n">
+        <v>548</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>130</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>157</v>
+      </c>
+      <c r="K75" t="n">
+        <v>146</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1529411764705882</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001484780994803314</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.789473684210526</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5399999999999991</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01962209302325579</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
